--- a/Proyecto/output/indicadores_acceso_tecnologico cambios.xlsx
+++ b/Proyecto/output/indicadores_acceso_tecnologico cambios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefanivilleda/Desktop/Programación II/Proyecto/programa-II/Proyecto/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112D51BA-D1AF-264E-AA33-3CBD2C8D28FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773D1E2D-6B49-7342-9442-9F51D60B0AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -699,7 +699,7 @@
         <v>99.15</v>
       </c>
       <c r="C2" s="1">
-        <v>89.38</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
         <v>91</v>
@@ -731,7 +731,7 @@
         <v>91.21</v>
       </c>
       <c r="C3" s="1">
-        <v>73.739999999999995</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1">
         <v>72</v>

--- a/Proyecto/output/indicadores_acceso_tecnologico cambios.xlsx
+++ b/Proyecto/output/indicadores_acceso_tecnologico cambios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefanivilleda/Desktop/Programación II/Proyecto/programa-II/Proyecto/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773D1E2D-6B49-7342-9442-9F51D60B0AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A364D7B-5BC5-604A-9CBA-17BD3C7B0956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <author>Stefani Villeda</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{CCBA4751-0619-2740-A3C7-29995EEF48C4}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{CCBA4751-0619-2740-A3C7-29995EEF48C4}">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{6D33F9FF-A80B-C948-A21E-346E459D4BD5}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{6D33F9FF-A80B-C948-A21E-346E459D4BD5}">
       <text>
         <r>
           <rPr>
@@ -102,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{38A12CE7-2052-774B-B8BE-2E77B12EA413}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{4EAF7E30-6F28-2E47-A074-3B251A7A37B5}">
       <text>
         <r>
           <rPr>
@@ -131,7 +131,40 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>por cada 100 habitantes</t>
+          <t>radiobase por cada 100,000 habitantes</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{38A12CE7-2052-774B-B8BE-2E77B12EA413}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Stefani Villeda:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>por cada 1000 habitantes</t>
         </r>
       </text>
     </comment>
@@ -140,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>depto</t>
   </si>
@@ -215,13 +248,23 @@
   </si>
   <si>
     <t>densidad_radiobases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lower </t>
+  </si>
+  <si>
+    <t>PIIB_per_capita</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +274,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -277,7 +327,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -285,11 +335,111 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -306,8 +456,41 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -644,115 +827,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="F1" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1">
-        <v>99.15</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="13">
         <v>93</v>
       </c>
-      <c r="D2" s="1">
+      <c r="C2" s="13">
         <v>91</v>
       </c>
-      <c r="E2" s="1">
+      <c r="D2" s="13">
         <v>94.39</v>
       </c>
-      <c r="F2" s="2">
+      <c r="E2" s="13">
         <v>15</v>
       </c>
-      <c r="G2" s="4">
+      <c r="F2" s="14">
         <v>90.32</v>
       </c>
-      <c r="H2" s="4">
+      <c r="G2" s="14">
         <v>80.8</v>
       </c>
-      <c r="I2" s="4">
+      <c r="H2" s="14">
         <v>136.16</v>
       </c>
-      <c r="J2" s="1">
-        <v>37.18</v>
+      <c r="I2" s="15">
+        <v>404.86327950600662</v>
+      </c>
+      <c r="J2" s="16">
+        <v>14654.86531187161</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="1">
-        <v>91.21</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="18">
         <v>77</v>
       </c>
-      <c r="D3" s="1">
+      <c r="C3" s="18">
         <v>72</v>
       </c>
-      <c r="E3" s="1">
+      <c r="D3" s="18">
         <v>83.4</v>
       </c>
-      <c r="F3" s="2">
+      <c r="E3" s="18">
         <v>18.2</v>
       </c>
-      <c r="G3" s="4">
+      <c r="F3" s="19">
         <v>66.2</v>
       </c>
-      <c r="H3" s="4">
+      <c r="G3" s="19">
         <v>42.91</v>
       </c>
-      <c r="I3" s="4">
+      <c r="H3" s="19">
         <v>79.430000000000007</v>
       </c>
-      <c r="J3" s="1">
-        <v>16.46</v>
+      <c r="I3" s="20">
+        <v>404.86327950600662</v>
+      </c>
+      <c r="J3" s="21">
+        <v>14654.86531187161</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -760,31 +943,31 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>73.849999999999994</v>
+        <v>56.4</v>
       </c>
       <c r="C4">
-        <v>56.4</v>
+        <v>30.73</v>
       </c>
       <c r="D4">
-        <v>30.73</v>
+        <v>69.2</v>
       </c>
       <c r="E4">
-        <v>69.2</v>
+        <v>10.24</v>
       </c>
       <c r="F4">
-        <v>10.24</v>
+        <v>36.880000000000003</v>
       </c>
       <c r="G4">
-        <v>36.880000000000003</v>
-      </c>
-      <c r="H4">
         <v>36.67</v>
       </c>
-      <c r="I4">
-        <v>31.28</v>
-      </c>
-      <c r="J4">
-        <v>76</v>
+      <c r="H4" s="7">
+        <v>167.7049777112282</v>
+      </c>
+      <c r="I4" s="7">
+        <v>404.86327950600662</v>
+      </c>
+      <c r="J4" s="7">
+        <v>14654.86531187161</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -792,31 +975,31 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>61.73</v>
+        <v>44.76</v>
       </c>
       <c r="C5">
-        <v>44.76</v>
+        <v>23.04</v>
       </c>
       <c r="D5">
-        <v>23.04</v>
+        <v>58.52</v>
       </c>
       <c r="E5">
-        <v>58.52</v>
+        <v>44.4</v>
       </c>
       <c r="F5">
-        <v>44.4</v>
+        <v>15.49</v>
       </c>
       <c r="G5">
-        <v>15.49</v>
-      </c>
-      <c r="H5">
         <v>13.53</v>
       </c>
-      <c r="I5">
-        <v>1.7</v>
-      </c>
-      <c r="J5">
-        <v>0.49</v>
+      <c r="H5" s="7">
+        <v>168.09112468705089</v>
+      </c>
+      <c r="I5" s="7">
+        <v>47.969449057216998</v>
+      </c>
+      <c r="J5" s="7">
+        <v>5502.5833595994081</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -824,31 +1007,31 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <v>68.87</v>
+        <v>47.32</v>
       </c>
       <c r="C6">
-        <v>47.32</v>
+        <v>22.53</v>
       </c>
       <c r="D6">
-        <v>22.53</v>
+        <v>66.05</v>
       </c>
       <c r="E6">
-        <v>66.05</v>
+        <v>12.8</v>
       </c>
       <c r="F6">
-        <v>12.8</v>
+        <v>15.62</v>
       </c>
       <c r="G6">
-        <v>15.62</v>
-      </c>
-      <c r="H6">
         <v>29.89</v>
       </c>
-      <c r="I6">
-        <v>2.79</v>
-      </c>
-      <c r="J6">
-        <v>1.1499999999999999</v>
+      <c r="H6" s="7">
+        <v>133.17795904777759</v>
+      </c>
+      <c r="I6" s="7">
+        <v>54.607859458083219</v>
+      </c>
+      <c r="J6" s="7">
+        <v>6413.809557371761</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -856,31 +1039,31 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>58.85</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="C7">
-        <v>36.799999999999997</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="D7">
-        <v>18.809999999999999</v>
+        <v>55.73</v>
       </c>
       <c r="E7">
-        <v>55.73</v>
+        <v>50.26</v>
       </c>
       <c r="F7">
-        <v>50.26</v>
+        <v>17.28</v>
       </c>
       <c r="G7">
-        <v>17.28</v>
-      </c>
-      <c r="H7">
         <v>14.9</v>
       </c>
-      <c r="I7">
-        <v>2.98</v>
-      </c>
-      <c r="J7">
-        <v>0.75</v>
+      <c r="H7" s="7">
+        <v>75.27008486993563</v>
+      </c>
+      <c r="I7" s="7">
+        <v>18.812339111812999</v>
+      </c>
+      <c r="J7" s="7">
+        <v>2841.710966594324</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -888,31 +1071,31 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>64.8</v>
+        <v>47.95</v>
       </c>
       <c r="C8">
-        <v>47.95</v>
+        <v>25.4</v>
       </c>
       <c r="D8">
-        <v>25.4</v>
+        <v>59.28</v>
       </c>
       <c r="E8">
-        <v>59.28</v>
+        <v>42.99</v>
       </c>
       <c r="F8">
-        <v>42.99</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="G8">
-        <v>16.350000000000001</v>
-      </c>
-      <c r="H8">
         <v>11.85</v>
       </c>
-      <c r="I8">
-        <v>5.53</v>
-      </c>
-      <c r="J8">
-        <v>1.28</v>
+      <c r="H8" s="7">
+        <v>130.9968385934412</v>
+      </c>
+      <c r="I8" s="7">
+        <v>30.043074771392909</v>
+      </c>
+      <c r="J8" s="7">
+        <v>10861.05517605828</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -920,31 +1103,31 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>62.88</v>
+        <v>44.69</v>
       </c>
       <c r="C9">
-        <v>44.69</v>
+        <v>21.98</v>
       </c>
       <c r="D9">
-        <v>21.98</v>
+        <v>58.33</v>
       </c>
       <c r="E9">
-        <v>58.33</v>
+        <v>54.36</v>
       </c>
       <c r="F9">
-        <v>54.36</v>
+        <v>17.95</v>
       </c>
       <c r="G9">
-        <v>17.95</v>
-      </c>
-      <c r="H9">
         <v>6.91</v>
       </c>
-      <c r="I9">
-        <v>3.13</v>
-      </c>
-      <c r="J9">
-        <v>0.51</v>
+      <c r="H9" s="7">
+        <v>133.50024511520411</v>
+      </c>
+      <c r="I9" s="7">
+        <v>21.567949436235029</v>
+      </c>
+      <c r="J9" s="7">
+        <v>4447.2811944283394</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -952,31 +1135,31 @@
         <v>7</v>
       </c>
       <c r="B10">
-        <v>55.61</v>
+        <v>35.840000000000003</v>
       </c>
       <c r="C10">
-        <v>35.840000000000003</v>
+        <v>17.82</v>
       </c>
       <c r="D10">
-        <v>17.82</v>
+        <v>53.3</v>
       </c>
       <c r="E10">
-        <v>53.3</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="F10">
-        <v>35.299999999999997</v>
+        <v>21.05</v>
       </c>
       <c r="G10">
-        <v>21.05</v>
-      </c>
-      <c r="H10">
         <v>17.03</v>
       </c>
-      <c r="I10">
-        <v>1.95</v>
-      </c>
-      <c r="J10">
-        <v>0.51</v>
+      <c r="H10" s="7">
+        <v>78.088812189233167</v>
+      </c>
+      <c r="I10" s="7">
+        <v>20.305140744323701</v>
+      </c>
+      <c r="J10" s="7">
+        <v>3253.97911654683</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -984,31 +1167,31 @@
         <v>8</v>
       </c>
       <c r="B11">
-        <v>51.39</v>
+        <v>32.520000000000003</v>
       </c>
       <c r="C11">
-        <v>32.520000000000003</v>
+        <v>16.309999999999999</v>
       </c>
       <c r="D11">
-        <v>16.309999999999999</v>
+        <v>48.51</v>
       </c>
       <c r="E11">
-        <v>48.51</v>
+        <v>50.41</v>
       </c>
       <c r="F11">
-        <v>50.41</v>
+        <v>17.02</v>
       </c>
       <c r="G11">
-        <v>17.02</v>
-      </c>
-      <c r="H11">
         <v>13.58</v>
       </c>
-      <c r="I11">
-        <v>1.75</v>
-      </c>
-      <c r="J11">
-        <v>0.65</v>
+      <c r="H11" s="7">
+        <v>67.335426900699929</v>
+      </c>
+      <c r="I11" s="7">
+        <v>24.892450359811381</v>
+      </c>
+      <c r="J11" s="7">
+        <v>3705.3634024380449</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1016,31 +1199,31 @@
         <v>9</v>
       </c>
       <c r="B12">
-        <v>61.85</v>
+        <v>44.65</v>
       </c>
       <c r="C12">
-        <v>44.65</v>
+        <v>23.89</v>
       </c>
       <c r="D12">
-        <v>23.89</v>
+        <v>58.31</v>
       </c>
       <c r="E12">
-        <v>58.31</v>
+        <v>43.76</v>
       </c>
       <c r="F12">
-        <v>43.76</v>
+        <v>25.74</v>
       </c>
       <c r="G12">
-        <v>25.74</v>
-      </c>
-      <c r="H12">
         <v>19.77</v>
       </c>
-      <c r="I12">
-        <v>5.58</v>
-      </c>
-      <c r="J12">
-        <v>7.46</v>
+      <c r="H12" s="7">
+        <v>116.4051111455224</v>
+      </c>
+      <c r="I12" s="7">
+        <v>154.42472914452921</v>
+      </c>
+      <c r="J12" s="7">
+        <v>7089.6459617951687</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1048,31 +1231,31 @@
         <v>10</v>
       </c>
       <c r="B13">
-        <v>55.43</v>
+        <v>39.049999999999997</v>
       </c>
       <c r="C13">
-        <v>39.049999999999997</v>
+        <v>19.04</v>
       </c>
       <c r="D13">
-        <v>19.04</v>
+        <v>52.36</v>
       </c>
       <c r="E13">
-        <v>52.36</v>
+        <v>50.69</v>
       </c>
       <c r="F13">
-        <v>50.69</v>
+        <v>12.35</v>
       </c>
       <c r="G13">
-        <v>12.35</v>
-      </c>
-      <c r="H13">
         <v>10.19</v>
       </c>
-      <c r="I13">
-        <v>3.33</v>
-      </c>
-      <c r="J13">
-        <v>0.75</v>
+      <c r="H13" s="7">
+        <v>103.7644132760979</v>
+      </c>
+      <c r="I13" s="7">
+        <v>23.163409794402789</v>
+      </c>
+      <c r="J13" s="7">
+        <v>4277.2875928465764</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1080,31 +1263,31 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>59.49</v>
+        <v>38.979999999999997</v>
       </c>
       <c r="C14">
-        <v>38.979999999999997</v>
+        <v>19.53</v>
       </c>
       <c r="D14">
-        <v>19.53</v>
+        <v>55.3</v>
       </c>
       <c r="E14">
-        <v>55.3</v>
+        <v>47.41</v>
       </c>
       <c r="F14">
-        <v>47.41</v>
+        <v>13.36</v>
       </c>
       <c r="G14">
-        <v>13.36</v>
-      </c>
-      <c r="H14">
         <v>10.97</v>
       </c>
-      <c r="I14">
-        <v>2.33</v>
-      </c>
-      <c r="J14">
-        <v>0.55000000000000004</v>
+      <c r="H14" s="7">
+        <v>117.3784783715934</v>
+      </c>
+      <c r="I14" s="7">
+        <v>27.741653588704779</v>
+      </c>
+      <c r="J14" s="7">
+        <v>5334.3289282319183</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -1112,31 +1295,31 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>53.99</v>
+        <v>36.119999999999997</v>
       </c>
       <c r="C15">
-        <v>36.119999999999997</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="D15">
-        <v>19.690000000000001</v>
+        <v>50.81</v>
       </c>
       <c r="E15">
-        <v>50.81</v>
+        <v>75.36</v>
       </c>
       <c r="F15">
-        <v>75.36</v>
+        <v>11.71</v>
       </c>
       <c r="G15">
-        <v>11.71</v>
-      </c>
-      <c r="H15">
         <v>10.95</v>
       </c>
-      <c r="I15">
-        <v>5.0599999999999996</v>
-      </c>
-      <c r="J15">
-        <v>1.07</v>
+      <c r="H15" s="7">
+        <v>80.706422415943067</v>
+      </c>
+      <c r="I15" s="7">
+        <v>17.042383546029239</v>
+      </c>
+      <c r="J15" s="7">
+        <v>4681.3897633864817</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1144,31 +1327,31 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>51.83</v>
+        <v>32.69</v>
       </c>
       <c r="C16">
-        <v>32.69</v>
+        <v>17.39</v>
       </c>
       <c r="D16">
-        <v>17.39</v>
+        <v>49.35</v>
       </c>
       <c r="E16">
-        <v>49.35</v>
+        <v>64.52</v>
       </c>
       <c r="F16">
-        <v>64.52</v>
+        <v>15.5</v>
       </c>
       <c r="G16">
-        <v>15.5</v>
-      </c>
-      <c r="H16">
         <v>12.22</v>
       </c>
-      <c r="I16">
-        <v>6.1</v>
-      </c>
-      <c r="J16">
-        <v>1.21</v>
+      <c r="H16" s="7">
+        <v>81.842121732934714</v>
+      </c>
+      <c r="I16" s="7">
+        <v>16.085759539593361</v>
+      </c>
+      <c r="J16" s="7">
+        <v>2860.3775419277249</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -1176,31 +1359,31 @@
         <v>14</v>
       </c>
       <c r="B17">
-        <v>48.67</v>
+        <v>27.64</v>
       </c>
       <c r="C17">
-        <v>27.64</v>
+        <v>14.43</v>
       </c>
       <c r="D17">
-        <v>14.43</v>
+        <v>46.65</v>
       </c>
       <c r="E17">
-        <v>46.65</v>
+        <v>63.33</v>
       </c>
       <c r="F17">
-        <v>63.33</v>
+        <v>8.48</v>
       </c>
       <c r="G17">
-        <v>8.48</v>
-      </c>
-      <c r="H17">
         <v>8.49</v>
       </c>
-      <c r="I17">
-        <v>3.88</v>
-      </c>
-      <c r="J17">
-        <v>0.48</v>
+      <c r="H17" s="7">
+        <v>67.713334971078893</v>
+      </c>
+      <c r="I17" s="7">
+        <v>8.3739419791410761</v>
+      </c>
+      <c r="J17" s="7">
+        <v>2601.343610276273</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1208,31 +1391,31 @@
         <v>15</v>
       </c>
       <c r="B18">
-        <v>53.31</v>
+        <v>29.8</v>
       </c>
       <c r="C18">
-        <v>29.8</v>
+        <v>16.079999999999998</v>
       </c>
       <c r="D18">
-        <v>16.079999999999998</v>
+        <v>50.71</v>
       </c>
       <c r="E18">
-        <v>50.71</v>
+        <v>65.260000000000005</v>
       </c>
       <c r="F18">
-        <v>65.260000000000005</v>
+        <v>10.07</v>
       </c>
       <c r="G18">
-        <v>10.07</v>
-      </c>
-      <c r="H18">
         <v>14.64</v>
       </c>
-      <c r="I18">
-        <v>1.56</v>
-      </c>
-      <c r="J18">
-        <v>0.25</v>
+      <c r="H18" s="7">
+        <v>88.494291392842129</v>
+      </c>
+      <c r="I18" s="7">
+        <v>14.324469396933161</v>
+      </c>
+      <c r="J18" s="7">
+        <v>2997.2282568044861</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -1240,31 +1423,31 @@
         <v>16</v>
       </c>
       <c r="B19">
-        <v>41.22</v>
+        <v>21.62</v>
       </c>
       <c r="C19">
-        <v>21.62</v>
+        <v>9.25</v>
       </c>
       <c r="D19">
-        <v>9.25</v>
+        <v>37.58</v>
       </c>
       <c r="E19">
-        <v>37.58</v>
+        <v>69.790000000000006</v>
       </c>
       <c r="F19">
-        <v>69.790000000000006</v>
+        <v>6.14</v>
       </c>
       <c r="G19">
-        <v>6.14</v>
-      </c>
-      <c r="H19">
         <v>7.36</v>
       </c>
-      <c r="I19">
-        <v>3.75</v>
-      </c>
-      <c r="J19">
-        <v>0.65</v>
+      <c r="H19" s="7">
+        <v>51.953590021499259</v>
+      </c>
+      <c r="I19" s="7">
+        <v>8.9380074980899415</v>
+      </c>
+      <c r="J19" s="7">
+        <v>3424.9822825369802</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1272,31 +1455,31 @@
         <v>17</v>
       </c>
       <c r="B20">
-        <v>56.74</v>
+        <v>42.63</v>
       </c>
       <c r="C20">
-        <v>42.63</v>
+        <v>22.49</v>
       </c>
       <c r="D20">
-        <v>22.49</v>
+        <v>52.29</v>
       </c>
       <c r="E20">
-        <v>52.29</v>
+        <v>63.06</v>
       </c>
       <c r="F20">
-        <v>63.06</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="G20">
-        <v>16.350000000000001</v>
-      </c>
-      <c r="H20">
         <v>13.88</v>
       </c>
-      <c r="I20">
-        <v>4.1900000000000004</v>
-      </c>
-      <c r="J20">
-        <v>0.63</v>
+      <c r="H20" s="7">
+        <v>127.782351351478</v>
+      </c>
+      <c r="I20" s="7">
+        <v>18.947092170441039</v>
+      </c>
+      <c r="J20" s="7">
+        <v>5385.8394952948338</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -1304,31 +1487,31 @@
         <v>18</v>
       </c>
       <c r="B21">
-        <v>56.4</v>
+        <v>41.53</v>
       </c>
       <c r="C21">
-        <v>41.53</v>
+        <v>21.34</v>
       </c>
       <c r="D21">
-        <v>21.34</v>
+        <v>51.11</v>
       </c>
       <c r="E21">
-        <v>51.11</v>
+        <v>63.21</v>
       </c>
       <c r="F21">
-        <v>63.21</v>
+        <v>24.37</v>
       </c>
       <c r="G21">
-        <v>24.37</v>
-      </c>
-      <c r="H21">
         <v>11.15</v>
       </c>
-      <c r="I21">
-        <v>3.16</v>
-      </c>
-      <c r="J21">
-        <v>1.06</v>
+      <c r="H21" s="7">
+        <v>134.68469156769049</v>
+      </c>
+      <c r="I21" s="7">
+        <v>45.015684108734433</v>
+      </c>
+      <c r="J21" s="7">
+        <v>6539.4225553021897</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1336,31 +1519,31 @@
         <v>19</v>
       </c>
       <c r="B22">
-        <v>57.78</v>
+        <v>41.67</v>
       </c>
       <c r="C22">
-        <v>41.67</v>
+        <v>21.28</v>
       </c>
       <c r="D22">
-        <v>21.28</v>
+        <v>55.41</v>
       </c>
       <c r="E22">
-        <v>55.41</v>
+        <v>57.12</v>
       </c>
       <c r="F22">
-        <v>57.12</v>
+        <v>19.760000000000002</v>
       </c>
       <c r="G22">
-        <v>19.760000000000002</v>
-      </c>
-      <c r="H22">
         <v>14.71</v>
       </c>
-      <c r="I22">
-        <v>1.8</v>
-      </c>
-      <c r="J22">
-        <v>0.71</v>
+      <c r="H22" s="7">
+        <v>127.5764461986206</v>
+      </c>
+      <c r="I22" s="7">
+        <v>49.986771192368607</v>
+      </c>
+      <c r="J22" s="7">
+        <v>7132.5969764371694</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -1368,31 +1551,31 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>52.25</v>
+        <v>34.24</v>
       </c>
       <c r="C23">
-        <v>34.24</v>
+        <v>17.23</v>
       </c>
       <c r="D23">
-        <v>17.23</v>
+        <v>50.4</v>
       </c>
       <c r="E23">
-        <v>50.4</v>
+        <v>64.180000000000007</v>
       </c>
       <c r="F23">
-        <v>64.180000000000007</v>
+        <v>24.74</v>
       </c>
       <c r="G23">
-        <v>24.74</v>
-      </c>
-      <c r="H23">
         <v>11.23</v>
       </c>
-      <c r="I23">
-        <v>2.5</v>
-      </c>
-      <c r="J23">
-        <v>0.66</v>
+      <c r="H23" s="7">
+        <v>106.2500272156832</v>
+      </c>
+      <c r="I23" s="7">
+        <v>27.659843150574581</v>
+      </c>
+      <c r="J23" s="7">
+        <v>4013.8238973598141</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1400,31 +1583,31 @@
         <v>21</v>
       </c>
       <c r="B24">
-        <v>52.17</v>
+        <v>32.76</v>
       </c>
       <c r="C24">
-        <v>32.76</v>
+        <v>19.16</v>
       </c>
       <c r="D24">
-        <v>19.16</v>
+        <v>49.28</v>
       </c>
       <c r="E24">
-        <v>49.28</v>
+        <v>42.43</v>
       </c>
       <c r="F24">
-        <v>42.43</v>
+        <v>20.309999999999999</v>
       </c>
       <c r="G24">
-        <v>20.309999999999999</v>
-      </c>
-      <c r="H24">
         <v>12.89</v>
       </c>
-      <c r="I24">
-        <v>2</v>
-      </c>
-      <c r="J24">
-        <v>0.47</v>
+      <c r="H24" s="7">
+        <v>94.2215607922342</v>
+      </c>
+      <c r="I24" s="7">
+        <v>21.79175585502443</v>
+      </c>
+      <c r="J24" s="7">
+        <v>3297.504029218479</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1432,31 +1615,149 @@
         <v>22</v>
       </c>
       <c r="B25">
-        <v>64.17</v>
+        <v>44.26</v>
       </c>
       <c r="C25">
-        <v>44.26</v>
+        <v>23.97</v>
       </c>
       <c r="D25">
-        <v>23.97</v>
+        <v>60.09</v>
       </c>
       <c r="E25">
-        <v>60.09</v>
+        <v>52.28</v>
       </c>
       <c r="F25">
-        <v>52.28</v>
+        <v>21.69</v>
       </c>
       <c r="G25">
-        <v>21.69</v>
-      </c>
-      <c r="H25">
         <v>9.56</v>
       </c>
-      <c r="I25">
-        <v>3.66</v>
-      </c>
-      <c r="J25">
-        <v>2.72</v>
+      <c r="H25" s="7">
+        <v>126.782490894712</v>
+      </c>
+      <c r="I25" s="7">
+        <v>93.563705098606633</v>
+      </c>
+      <c r="J25" s="7">
+        <v>3875.954919188006</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B28" s="6">
+        <f t="shared" ref="B28:I28" si="0">MIN(B4:B25)</f>
+        <v>21.62</v>
+      </c>
+      <c r="C28" s="6">
+        <f t="shared" si="0"/>
+        <v>9.25</v>
+      </c>
+      <c r="D28" s="6">
+        <f t="shared" si="0"/>
+        <v>37.58</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="0"/>
+        <v>10.24</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" ref="F28:H28" si="1">MIN(F4:F25)</f>
+        <v>6.14</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" si="1"/>
+        <v>6.91</v>
+      </c>
+      <c r="H28" s="6">
+        <f t="shared" si="1"/>
+        <v>51.953590021499259</v>
+      </c>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6">
+        <f t="shared" ref="J28" si="2">MIN(J4:J25)</f>
+        <v>2601.343610276273</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B29" s="6">
+        <f t="shared" ref="B29:I29" si="3">STDEV(B4:B25)</f>
+        <v>7.8238260809820712</v>
+      </c>
+      <c r="C29" s="6">
+        <f t="shared" si="3"/>
+        <v>4.3777721952997304</v>
+      </c>
+      <c r="D29" s="6">
+        <f t="shared" si="3"/>
+        <v>6.7320008057400029</v>
+      </c>
+      <c r="E29" s="6">
+        <f>STDEV(E4:E25)*1/2</f>
+        <v>8.1779116238889742</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" ref="F29:H29" si="4">STDEV(F4:F25)*1/2</f>
+        <v>3.3510700704227476</v>
+      </c>
+      <c r="G29" s="6">
+        <f t="shared" si="4"/>
+        <v>3.4716735690628941</v>
+      </c>
+      <c r="H29" s="6">
+        <f t="shared" si="4"/>
+        <v>15.957653889085258</v>
+      </c>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6">
+        <f t="shared" ref="J29" si="5">STDEV(J4:J25)*1/2</f>
+        <v>1432.6525698165146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="9">
+        <f>B28-B29</f>
+        <v>13.79617391901793</v>
+      </c>
+      <c r="C30" s="9">
+        <f t="shared" ref="C30:H30" si="6">C28-C29</f>
+        <v>4.8722278047002696</v>
+      </c>
+      <c r="D30" s="9">
+        <f t="shared" si="6"/>
+        <v>30.847999194259994</v>
+      </c>
+      <c r="E30" s="9">
+        <f t="shared" si="6"/>
+        <v>2.062088376111026</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="6"/>
+        <v>2.7889299295772521</v>
+      </c>
+      <c r="G30" s="9">
+        <f t="shared" si="6"/>
+        <v>3.438326430937106</v>
+      </c>
+      <c r="H30" s="9">
+        <f t="shared" si="6"/>
+        <v>35.995936132414002</v>
+      </c>
+      <c r="I30" s="10">
+        <v>8.3739419791410761</v>
+      </c>
+      <c r="J30" s="11">
+        <f t="shared" ref="J30" si="7">J28-J29</f>
+        <v>1168.6910404597584</v>
       </c>
     </row>
   </sheetData>
